--- a/Base_UC_2025_V2.xlsx
+++ b/Base_UC_2025_V2.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22003B1F-D7CC-3D40-8CBB-0AAD1BB0D4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0779C696-830F-EB45-A8BE-E64A639AA84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{A22C7B05-6B0A-4116-A99A-60EDDEA67682}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="460">
   <si>
     <t>ID</t>
   </si>
@@ -1384,6 +1384,36 @@
   </si>
   <si>
     <t>DA | División de Equipo y Mobiliario Médico (Especial)</t>
+  </si>
+  <si>
+    <t>COAHUILA (UMAE)</t>
+  </si>
+  <si>
+    <t>YUCATAN (UMAE)</t>
+  </si>
+  <si>
+    <t>PUEBLA (UMAE)</t>
+  </si>
+  <si>
+    <t>CIUDAD DE MEXICO (UMAE)</t>
+  </si>
+  <si>
+    <t>JALISCO (UMAE)</t>
+  </si>
+  <si>
+    <t>GUANAJUATO (UMAE)</t>
+  </si>
+  <si>
+    <t>NUEVO LEON (UMAE)</t>
+  </si>
+  <si>
+    <t>VERACRUZ (UMAE)</t>
+  </si>
+  <si>
+    <t>ESTADO DE MEXICO (UMAE)</t>
+  </si>
+  <si>
+    <t>SONORA (UMAE)</t>
   </si>
 </sst>
 </file>
@@ -1499,7 +1529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1511,9 +1541,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
@@ -2103,26 +2131,26 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="11">
+      <c r="A11" s="2">
         <v>133</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>448</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4431,7 +4459,7 @@
         <v>69</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>86</v>
+        <v>450</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>70</v>
@@ -4457,7 +4485,7 @@
         <v>69</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>40</v>
+        <v>451</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>70</v>
@@ -4483,7 +4511,7 @@
         <v>69</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>25</v>
+        <v>452</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>70</v>
@@ -4509,7 +4537,7 @@
         <v>69</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>70</v>
@@ -4535,7 +4563,7 @@
         <v>69</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>13</v>
+        <v>454</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>70</v>
@@ -4561,7 +4589,7 @@
         <v>69</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>70</v>
@@ -4587,7 +4615,7 @@
         <v>69</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>70</v>
@@ -4613,7 +4641,7 @@
         <v>69</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>89</v>
+        <v>455</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>70</v>
@@ -4639,7 +4667,7 @@
         <v>69</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>89</v>
+        <v>455</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>70</v>
@@ -4665,7 +4693,7 @@
         <v>69</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>40</v>
+        <v>451</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>70</v>
@@ -4691,7 +4719,7 @@
         <v>69</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>70</v>
@@ -4717,7 +4745,7 @@
         <v>69</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>70</v>
@@ -4743,7 +4771,7 @@
         <v>69</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>70</v>
@@ -4769,7 +4797,7 @@
         <v>69</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>49</v>
+        <v>457</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>70</v>
@@ -4795,7 +4823,7 @@
         <v>69</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>13</v>
+        <v>454</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>70</v>
@@ -4821,7 +4849,7 @@
         <v>69</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>70</v>
@@ -4847,7 +4875,7 @@
         <v>69</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>70</v>
@@ -4873,7 +4901,7 @@
         <v>69</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>70</v>
@@ -4899,7 +4927,7 @@
         <v>69</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>89</v>
+        <v>455</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>70</v>
@@ -4925,7 +4953,7 @@
         <v>69</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>70</v>
@@ -4951,7 +4979,7 @@
         <v>69</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>70</v>
@@ -4977,7 +5005,7 @@
         <v>69</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>13</v>
+        <v>454</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>70</v>
@@ -5003,7 +5031,7 @@
         <v>69</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>13</v>
+        <v>454</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>70</v>
@@ -5029,7 +5057,7 @@
         <v>69</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>70</v>
@@ -5055,7 +5083,7 @@
         <v>69</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>25</v>
+        <v>452</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>70</v>
@@ -5081,7 +5109,7 @@
         <v>69</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>70</v>
@@ -5107,7 +5135,7 @@
         <v>69</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>70</v>
@@ -5133,7 +5161,7 @@
         <v>69</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>70</v>
@@ -5159,7 +5187,7 @@
         <v>69</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>70</v>
@@ -5185,7 +5213,7 @@
         <v>69</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>70</v>
@@ -5211,7 +5239,7 @@
         <v>69</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>70</v>
@@ -5237,7 +5265,7 @@
         <v>69</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>70</v>
@@ -5263,7 +5291,7 @@
         <v>69</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>49</v>
+        <v>457</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>70</v>
@@ -5289,7 +5317,7 @@
         <v>69</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>101</v>
+        <v>459</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>70</v>
@@ -5299,28 +5327,28 @@
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" s="9">
+      <c r="A134">
         <v>84</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="B134" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C134" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="D134" s="9" t="s">
+      <c r="D134" t="s">
         <v>398</v>
       </c>
-      <c r="E134" s="9" t="s">
+      <c r="E134" t="s">
         <v>69</v>
       </c>
-      <c r="F134" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G134" s="12" t="s">
+      <c r="F134" t="s">
+        <v>456</v>
+      </c>
+      <c r="G134" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="H134" s="13" t="s">
+      <c r="H134" s="11" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5585,15 +5613,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="10d6067c-7057-404a-af3a-fb68dad60af1">
@@ -5602,6 +5621,15 @@
     <TaxCatchAll xmlns="2821cf9a-77cb-46bf-ae5e-824aab80feb9" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5624,14 +5652,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{276F6B04-42DF-4477-A764-6929D452E30E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E0E5B4-AAE0-478E-8C0D-38036984645F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5640,4 +5660,12 @@
     <ds:schemaRef ds:uri="2821cf9a-77cb-46bf-ae5e-824aab80feb9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{276F6B04-42DF-4477-A764-6929D452E30E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base_UC_2025_V2.xlsx
+++ b/Base_UC_2025_V2.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0779C696-830F-EB45-A8BE-E64A639AA84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22003B1F-D7CC-3D40-8CBB-0AAD1BB0D4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{A22C7B05-6B0A-4116-A99A-60EDDEA67682}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="450">
   <si>
     <t>ID</t>
   </si>
@@ -1384,36 +1384,6 @@
   </si>
   <si>
     <t>DA | División de Equipo y Mobiliario Médico (Especial)</t>
-  </si>
-  <si>
-    <t>COAHUILA (UMAE)</t>
-  </si>
-  <si>
-    <t>YUCATAN (UMAE)</t>
-  </si>
-  <si>
-    <t>PUEBLA (UMAE)</t>
-  </si>
-  <si>
-    <t>CIUDAD DE MEXICO (UMAE)</t>
-  </si>
-  <si>
-    <t>JALISCO (UMAE)</t>
-  </si>
-  <si>
-    <t>GUANAJUATO (UMAE)</t>
-  </si>
-  <si>
-    <t>NUEVO LEON (UMAE)</t>
-  </si>
-  <si>
-    <t>VERACRUZ (UMAE)</t>
-  </si>
-  <si>
-    <t>ESTADO DE MEXICO (UMAE)</t>
-  </si>
-  <si>
-    <t>SONORA (UMAE)</t>
   </si>
 </sst>
 </file>
@@ -1529,7 +1499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1541,7 +1511,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
@@ -2131,26 +2103,26 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
+      <c r="A11" s="11">
         <v>133</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>448</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="11" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4459,7 +4431,7 @@
         <v>69</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>450</v>
+        <v>86</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>70</v>
@@ -4485,7 +4457,7 @@
         <v>69</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>451</v>
+        <v>40</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>70</v>
@@ -4511,7 +4483,7 @@
         <v>69</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>452</v>
+        <v>25</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>70</v>
@@ -4537,7 +4509,7 @@
         <v>69</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>70</v>
@@ -4563,7 +4535,7 @@
         <v>69</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>454</v>
+        <v>13</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>70</v>
@@ -4589,7 +4561,7 @@
         <v>69</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>70</v>
@@ -4615,7 +4587,7 @@
         <v>69</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>70</v>
@@ -4641,7 +4613,7 @@
         <v>69</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>455</v>
+        <v>89</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>70</v>
@@ -4667,7 +4639,7 @@
         <v>69</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>455</v>
+        <v>89</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>70</v>
@@ -4693,7 +4665,7 @@
         <v>69</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>451</v>
+        <v>40</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>70</v>
@@ -4719,7 +4691,7 @@
         <v>69</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>70</v>
@@ -4745,7 +4717,7 @@
         <v>69</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>456</v>
+        <v>113</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>70</v>
@@ -4771,7 +4743,7 @@
         <v>69</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>456</v>
+        <v>113</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>70</v>
@@ -4797,7 +4769,7 @@
         <v>69</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>457</v>
+        <v>49</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>70</v>
@@ -4823,7 +4795,7 @@
         <v>69</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>454</v>
+        <v>13</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>70</v>
@@ -4849,7 +4821,7 @@
         <v>69</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>70</v>
@@ -4875,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>70</v>
@@ -4901,7 +4873,7 @@
         <v>69</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>70</v>
@@ -4927,7 +4899,7 @@
         <v>69</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>455</v>
+        <v>89</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>70</v>
@@ -4953,7 +4925,7 @@
         <v>69</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>70</v>
@@ -4979,7 +4951,7 @@
         <v>69</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>70</v>
@@ -5005,7 +4977,7 @@
         <v>69</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>454</v>
+        <v>13</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>70</v>
@@ -5031,7 +5003,7 @@
         <v>69</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>454</v>
+        <v>13</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>70</v>
@@ -5057,7 +5029,7 @@
         <v>69</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>70</v>
@@ -5083,7 +5055,7 @@
         <v>69</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>452</v>
+        <v>25</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>70</v>
@@ -5109,7 +5081,7 @@
         <v>69</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>70</v>
@@ -5135,7 +5107,7 @@
         <v>69</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>458</v>
+        <v>79</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>70</v>
@@ -5161,7 +5133,7 @@
         <v>69</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>458</v>
+        <v>79</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>70</v>
@@ -5187,7 +5159,7 @@
         <v>69</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>456</v>
+        <v>113</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>70</v>
@@ -5213,7 +5185,7 @@
         <v>69</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>456</v>
+        <v>113</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>70</v>
@@ -5239,7 +5211,7 @@
         <v>69</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>70</v>
@@ -5265,7 +5237,7 @@
         <v>69</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>456</v>
+        <v>113</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>70</v>
@@ -5291,7 +5263,7 @@
         <v>69</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>457</v>
+        <v>49</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>70</v>
@@ -5317,7 +5289,7 @@
         <v>69</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>459</v>
+        <v>101</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>70</v>
@@ -5327,28 +5299,28 @@
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134">
+      <c r="A134" s="9">
         <v>84</v>
       </c>
-      <c r="B134" s="9" t="s">
+      <c r="B134" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C134" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F134" t="s">
-        <v>456</v>
-      </c>
-      <c r="G134" s="10" t="s">
+      <c r="F134" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G134" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="H134" s="11" t="s">
+      <c r="H134" s="13" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5613,6 +5585,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="10d6067c-7057-404a-af3a-fb68dad60af1">
@@ -5621,15 +5602,6 @@
     <TaxCatchAll xmlns="2821cf9a-77cb-46bf-ae5e-824aab80feb9" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5652,6 +5624,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{276F6B04-42DF-4477-A764-6929D452E30E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E0E5B4-AAE0-478E-8C0D-38036984645F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5660,12 +5640,4 @@
     <ds:schemaRef ds:uri="2821cf9a-77cb-46bf-ae5e-824aab80feb9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{276F6B04-42DF-4477-A764-6929D452E30E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base_UC_2025_V2.xlsx
+++ b/Base_UC_2025_V2.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22003B1F-D7CC-3D40-8CBB-0AAD1BB0D4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AE3F67-5CED-FE4D-93F9-6CC285869C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{A22C7B05-6B0A-4116-A99A-60EDDEA67682}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="460">
   <si>
     <t>ID</t>
   </si>
@@ -1384,6 +1384,36 @@
   </si>
   <si>
     <t>DA | División de Equipo y Mobiliario Médico (Especial)</t>
+  </si>
+  <si>
+    <t>COAHUILA (UMAE)</t>
+  </si>
+  <si>
+    <t>YUCATAN (UMAE)</t>
+  </si>
+  <si>
+    <t>PUEBLA (UMAE)</t>
+  </si>
+  <si>
+    <t>CIUDAD DE MEXICO (UMAE)</t>
+  </si>
+  <si>
+    <t>JALISCO (UMAE)</t>
+  </si>
+  <si>
+    <t>GUANAJUATO (UMAE)</t>
+  </si>
+  <si>
+    <t>NUEVO LEON (UMAE)</t>
+  </si>
+  <si>
+    <t>VERACRUZ (UMAE)</t>
+  </si>
+  <si>
+    <t>ESTADO DE MEXICO (UMAE)</t>
+  </si>
+  <si>
+    <t>SONORA (UMAE)</t>
   </si>
 </sst>
 </file>
@@ -1499,7 +1529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1511,9 +1541,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
@@ -1914,7 +1942,7 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>10</v>
@@ -2103,26 +2131,26 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="11">
+      <c r="A11" s="2">
         <v>133</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>448</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4431,7 +4459,7 @@
         <v>69</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>86</v>
+        <v>450</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>70</v>
@@ -4457,7 +4485,7 @@
         <v>69</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>40</v>
+        <v>451</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>70</v>
@@ -4483,7 +4511,7 @@
         <v>69</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>25</v>
+        <v>452</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>70</v>
@@ -4509,7 +4537,7 @@
         <v>69</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>70</v>
@@ -4535,7 +4563,7 @@
         <v>69</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>13</v>
+        <v>454</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>70</v>
@@ -4561,7 +4589,7 @@
         <v>69</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>70</v>
@@ -4587,7 +4615,7 @@
         <v>69</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>70</v>
@@ -4613,7 +4641,7 @@
         <v>69</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>89</v>
+        <v>455</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>70</v>
@@ -4639,7 +4667,7 @@
         <v>69</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>89</v>
+        <v>455</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>70</v>
@@ -4665,7 +4693,7 @@
         <v>69</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>40</v>
+        <v>451</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>70</v>
@@ -4691,7 +4719,7 @@
         <v>69</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>70</v>
@@ -4717,7 +4745,7 @@
         <v>69</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>70</v>
@@ -4743,7 +4771,7 @@
         <v>69</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>70</v>
@@ -4769,7 +4797,7 @@
         <v>69</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>49</v>
+        <v>457</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>70</v>
@@ -4795,7 +4823,7 @@
         <v>69</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>13</v>
+        <v>454</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>70</v>
@@ -4821,7 +4849,7 @@
         <v>69</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>70</v>
@@ -4847,7 +4875,7 @@
         <v>69</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>70</v>
@@ -4873,7 +4901,7 @@
         <v>69</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>70</v>
@@ -4899,7 +4927,7 @@
         <v>69</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>89</v>
+        <v>455</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>70</v>
@@ -4925,7 +4953,7 @@
         <v>69</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>70</v>
@@ -4951,7 +4979,7 @@
         <v>69</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>70</v>
@@ -4977,7 +5005,7 @@
         <v>69</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>13</v>
+        <v>454</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>70</v>
@@ -5003,7 +5031,7 @@
         <v>69</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>13</v>
+        <v>454</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>70</v>
@@ -5029,7 +5057,7 @@
         <v>69</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>70</v>
@@ -5055,7 +5083,7 @@
         <v>69</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>25</v>
+        <v>452</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>70</v>
@@ -5081,7 +5109,7 @@
         <v>69</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>70</v>
@@ -5107,7 +5135,7 @@
         <v>69</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>70</v>
@@ -5133,7 +5161,7 @@
         <v>69</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>70</v>
@@ -5159,7 +5187,7 @@
         <v>69</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>70</v>
@@ -5185,7 +5213,7 @@
         <v>69</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>70</v>
@@ -5211,7 +5239,7 @@
         <v>69</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>70</v>
@@ -5237,7 +5265,7 @@
         <v>69</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>113</v>
+        <v>456</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>70</v>
@@ -5263,7 +5291,7 @@
         <v>69</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>49</v>
+        <v>457</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>70</v>
@@ -5289,7 +5317,7 @@
         <v>69</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>101</v>
+        <v>459</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>70</v>
@@ -5299,28 +5327,28 @@
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" s="9">
+      <c r="A134">
         <v>84</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="B134" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C134" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="D134" s="9" t="s">
+      <c r="D134" t="s">
         <v>398</v>
       </c>
-      <c r="E134" s="9" t="s">
+      <c r="E134" t="s">
         <v>69</v>
       </c>
-      <c r="F134" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G134" s="12" t="s">
+      <c r="F134" t="s">
+        <v>456</v>
+      </c>
+      <c r="G134" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="H134" s="13" t="s">
+      <c r="H134" s="11" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5342,6 +5370,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="10d6067c-7057-404a-af3a-fb68dad60af1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2821cf9a-77cb-46bf-ae5e-824aab80feb9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101001E32C277C4DB6E4BA8E78B0FF6C742BD" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="57cef40b6fe73b8b241da2d44106d8ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="10d6067c-7057-404a-af3a-fb68dad60af1" xmlns:ns3="2821cf9a-77cb-46bf-ae5e-824aab80feb9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="da31e404c8a84745e3fd4df3e3a11000" ns2:_="" ns3:_="">
     <xsd:import namespace="10d6067c-7057-404a-af3a-fb68dad60af1"/>
@@ -5584,27 +5632,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{276F6B04-42DF-4477-A764-6929D452E30E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="10d6067c-7057-404a-af3a-fb68dad60af1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2821cf9a-77cb-46bf-ae5e-824aab80feb9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E0E5B4-AAE0-478E-8C0D-38036984645F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="10d6067c-7057-404a-af3a-fb68dad60af1"/>
+    <ds:schemaRef ds:uri="2821cf9a-77cb-46bf-ae5e-824aab80feb9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13F23DA0-3680-4908-9023-5E164847111E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5621,23 +5668,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{276F6B04-42DF-4477-A764-6929D452E30E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E0E5B4-AAE0-478E-8C0D-38036984645F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="10d6067c-7057-404a-af3a-fb68dad60af1"/>
-    <ds:schemaRef ds:uri="2821cf9a-77cb-46bf-ae5e-824aab80feb9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base_UC_2025_V2.xlsx
+++ b/Base_UC_2025_V2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AE3F67-5CED-FE4D-93F9-6CC285869C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8800140-557A-6A47-96E9-50678668AD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{A22C7B05-6B0A-4116-A99A-60EDDEA67682}"/>
   </bookViews>
@@ -1107,9 +1107,6 @@
     <t>UMAE Hospital General Dr. Gaudencio González CMN La Raza | Departamento de Abastecimiento</t>
   </si>
   <si>
-    <t>UMAE No. 14 CMN Adolfo Ruiz Cortinez  | Departamento de Abastecimiento</t>
-  </si>
-  <si>
     <t xml:space="preserve">OOAD Oaxaca | Departamento de Construcción y Planeación Inmobiliaria </t>
   </si>
   <si>
@@ -1414,6 +1411,9 @@
   </si>
   <si>
     <t>SONORA (UMAE)</t>
+  </si>
+  <si>
+    <t>UMAE HE 14 CMN Adolfo Ruiz Cortinez Veracruz  | Departamento de Abastecimiento</t>
   </si>
 </sst>
 </file>
@@ -1907,7 +1907,7 @@
         <v>253</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>254</v>
@@ -1933,7 +1933,7 @@
         <v>212</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -1959,7 +1959,7 @@
         <v>276</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>66</v>
@@ -1985,7 +1985,7 @@
         <v>286</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>66</v>
@@ -2011,7 +2011,7 @@
         <v>258</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>66</v>
@@ -2037,7 +2037,7 @@
         <v>138</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>66</v>
@@ -2089,7 +2089,7 @@
         <v>266</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>66</v>
@@ -2135,11 +2135,11 @@
         <v>133</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>66</v>
@@ -2165,7 +2165,7 @@
         <v>282</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>66</v>
@@ -2191,7 +2191,7 @@
         <v>290</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>66</v>
@@ -2217,7 +2217,7 @@
         <v>256</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>66</v>
@@ -2243,7 +2243,7 @@
         <v>288</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>66</v>
@@ -2295,7 +2295,7 @@
         <v>268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -2321,7 +2321,7 @@
         <v>239</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -2347,7 +2347,7 @@
         <v>237</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -2425,7 +2425,7 @@
         <v>183</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -2451,7 +2451,7 @@
         <v>314</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>254</v>
@@ -2477,7 +2477,7 @@
         <v>180</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -2503,7 +2503,7 @@
         <v>233</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>5</v>
@@ -2555,7 +2555,7 @@
         <v>231</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>5</v>
@@ -2607,7 +2607,7 @@
         <v>225</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>5</v>
@@ -2633,7 +2633,7 @@
         <v>264</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
@@ -2659,7 +2659,7 @@
         <v>294</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>5</v>
@@ -2685,7 +2685,7 @@
         <v>156</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>5</v>
@@ -2763,7 +2763,7 @@
         <v>168</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>5</v>
@@ -2815,7 +2815,7 @@
         <v>306</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>5</v>
@@ -2841,7 +2841,7 @@
         <v>187</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>5</v>
@@ -2893,7 +2893,7 @@
         <v>202</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>5</v>
@@ -2945,7 +2945,7 @@
         <v>152</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>5</v>
@@ -2997,7 +2997,7 @@
         <v>174</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>5</v>
@@ -3049,7 +3049,7 @@
         <v>292</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>5</v>
@@ -3075,7 +3075,7 @@
         <v>227</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>5</v>
@@ -3101,7 +3101,7 @@
         <v>229</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>5</v>
@@ -3179,7 +3179,7 @@
         <v>278</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>5</v>
@@ -3205,7 +3205,7 @@
         <v>221</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>5</v>
@@ -3257,7 +3257,7 @@
         <v>210</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>5</v>
@@ -3283,7 +3283,7 @@
         <v>298</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>5</v>
@@ -3335,7 +3335,7 @@
         <v>12</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>5</v>
@@ -3387,7 +3387,7 @@
         <v>148</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>5</v>
@@ -3439,7 +3439,7 @@
         <v>247</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>5</v>
@@ -3491,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>5</v>
@@ -3517,7 +3517,7 @@
         <v>150</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>5</v>
@@ -3569,7 +3569,7 @@
         <v>274</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>5</v>
@@ -3595,7 +3595,7 @@
         <v>140</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>5</v>
@@ -3647,7 +3647,7 @@
         <v>132</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>5</v>
@@ -3699,7 +3699,7 @@
         <v>198</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>5</v>
@@ -3725,7 +3725,7 @@
         <v>193</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>5</v>
@@ -3751,7 +3751,7 @@
         <v>249</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>5</v>
@@ -3777,7 +3777,7 @@
         <v>218</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>5</v>
@@ -3803,7 +3803,7 @@
         <v>270</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>5</v>
@@ -3829,7 +3829,7 @@
         <v>241</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>5</v>
@@ -3907,7 +3907,7 @@
         <v>189</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>5</v>
@@ -3933,7 +3933,7 @@
         <v>260</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>5</v>
@@ -3985,7 +3985,7 @@
         <v>166</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>5</v>
@@ -4037,7 +4037,7 @@
         <v>178</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>5</v>
@@ -4089,7 +4089,7 @@
         <v>208</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>5</v>
@@ -4193,7 +4193,7 @@
         <v>235</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>5</v>
@@ -4245,7 +4245,7 @@
         <v>308</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>5</v>
@@ -4297,7 +4297,7 @@
         <v>272</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>5</v>
@@ -4323,7 +4323,7 @@
         <v>172</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>5</v>
@@ -4375,7 +4375,7 @@
         <v>214</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>5</v>
@@ -4427,7 +4427,7 @@
         <v>204</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>5</v>
@@ -4453,13 +4453,13 @@
         <v>134</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>70</v>
@@ -4479,13 +4479,13 @@
         <v>170</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>70</v>
@@ -4505,13 +4505,13 @@
         <v>136</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>70</v>
@@ -4531,13 +4531,13 @@
         <v>302</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>70</v>
@@ -4563,7 +4563,7 @@
         <v>69</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>70</v>
@@ -4583,13 +4583,13 @@
         <v>154</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>70</v>
@@ -4609,13 +4609,13 @@
         <v>310</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>70</v>
@@ -4635,13 +4635,13 @@
         <v>251</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>70</v>
@@ -4661,13 +4661,13 @@
         <v>160</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>70</v>
@@ -4687,13 +4687,13 @@
         <v>284</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>70</v>
@@ -4713,13 +4713,13 @@
         <v>158</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>70</v>
@@ -4739,13 +4739,13 @@
         <v>196</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>70</v>
@@ -4765,13 +4765,13 @@
         <v>304</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>70</v>
@@ -4791,13 +4791,13 @@
         <v>300</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>70</v>
@@ -4817,13 +4817,13 @@
         <v>200</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>70</v>
@@ -4843,13 +4843,13 @@
         <v>144</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>70</v>
@@ -4875,7 +4875,7 @@
         <v>69</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>70</v>
@@ -4895,13 +4895,13 @@
         <v>245</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>70</v>
@@ -4921,13 +4921,13 @@
         <v>191</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>70</v>
@@ -4947,13 +4947,13 @@
         <v>146</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>70</v>
@@ -4973,13 +4973,13 @@
         <v>312</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>70</v>
@@ -4999,13 +4999,13 @@
         <v>243</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>70</v>
@@ -5025,13 +5025,13 @@
         <v>164</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>70</v>
@@ -5051,13 +5051,13 @@
         <v>176</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>70</v>
@@ -5077,13 +5077,13 @@
         <v>223</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>70</v>
@@ -5103,13 +5103,13 @@
         <v>142</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>70</v>
@@ -5129,13 +5129,13 @@
         <v>185</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>70</v>
@@ -5155,13 +5155,13 @@
         <v>296</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>70</v>
@@ -5181,13 +5181,13 @@
         <v>280</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>70</v>
@@ -5207,13 +5207,13 @@
         <v>206</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>70</v>
@@ -5239,7 +5239,7 @@
         <v>69</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>70</v>
@@ -5259,13 +5259,13 @@
         <v>162</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>70</v>
@@ -5285,13 +5285,13 @@
         <v>121</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>357</v>
+        <v>459</v>
       </c>
       <c r="E132" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>70</v>
@@ -5317,7 +5317,7 @@
         <v>69</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>70</v>
@@ -5337,13 +5337,13 @@
         <v>216</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E134" t="s">
         <v>69</v>
       </c>
       <c r="F134" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G134" s="10" t="s">
         <v>70</v>
@@ -5370,26 +5370,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="10d6067c-7057-404a-af3a-fb68dad60af1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2821cf9a-77cb-46bf-ae5e-824aab80feb9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101001E32C277C4DB6E4BA8E78B0FF6C742BD" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="57cef40b6fe73b8b241da2d44106d8ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="10d6067c-7057-404a-af3a-fb68dad60af1" xmlns:ns3="2821cf9a-77cb-46bf-ae5e-824aab80feb9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="da31e404c8a84745e3fd4df3e3a11000" ns2:_="" ns3:_="">
     <xsd:import namespace="10d6067c-7057-404a-af3a-fb68dad60af1"/>
@@ -5632,10 +5612,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="10d6067c-7057-404a-af3a-fb68dad60af1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2821cf9a-77cb-46bf-ae5e-824aab80feb9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{276F6B04-42DF-4477-A764-6929D452E30E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13F23DA0-3680-4908-9023-5E164847111E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="10d6067c-7057-404a-af3a-fb68dad60af1"/>
+    <ds:schemaRef ds:uri="2821cf9a-77cb-46bf-ae5e-824aab80feb9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5652,20 +5663,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13F23DA0-3680-4908-9023-5E164847111E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{276F6B04-42DF-4477-A764-6929D452E30E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="10d6067c-7057-404a-af3a-fb68dad60af1"/>
-    <ds:schemaRef ds:uri="2821cf9a-77cb-46bf-ae5e-824aab80feb9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>